--- a/public/docs/pdf-md-pdf/complete data of Kattakada (1)/tourists spot.xlsx
+++ b/public/docs/pdf-md-pdf/complete data of Kattakada (1)/tourists spot.xlsx
@@ -1,43 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tourists spot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tourists spot" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -211,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -279,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -414,157 +351,134 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Column1</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Column2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column3</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Attraction</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Type / Highlights</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Details</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Attraction</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Type / Highlights</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
+      <c r="A2" t="str">
+        <v>Neyyar Dam &amp; Wildlife Sanctuary</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dam, Wildlife Sanctuary, Boat rides, Trekking, Crocodile farm</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Located ~10 km east of Kattakada in the Agasthyamalai foothills. Sanctuary established in 1958; spans 128 km². Features elephants, leopards, gaur, Nilgiri langurs, crocodile farm (since 1977), gardens, trekking and boating options. (Thiruvananthapuram District)</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Neyyar Dam &amp; Wildlife Sanctuary</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dam, Wildlife Sanctuary, Boat rides, Trekking, Crocodile farm</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Located ~10 km east of Kattakada in the Agasthyamalai foothills. Sanctuary established in 1958; spans 128 km². Features elephants, leopards, gaur, Nilgiri langurs, crocodile farm (since 1977), gardens, trekking and boating options. (Thiruvananthapuram District)</t>
-        </is>
+      <c r="A3" t="str">
+        <v>Thoongampara (Hanging Rock)</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Eco-tourism, Scenic Cliff, Sunset Views</v>
+      </c>
+      <c r="C3" t="str">
+        <v>About 2 km from Kattakada on the Neyyattinkara road. A natural 200‑ft high overhang rock offering panoramic views. Undergoing development (₹99.99 lakhs) for eco-tourism with infrastructure upgrades. Nearby cultural sites: Irayankot Mahadeva Temple and St. Theresa Shrine. (Travel And Tour World, Curly Tales)</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thoongampara (Hanging Rock)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eco-tourism, Scenic Cliff, Sunset Views</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>About 2 km from Kattakada on the Neyyattinkara road. A natural 200‑ft high overhang rock offering panoramic views. Undergoing development (₹99.99 lakhs) for eco-tourism with infrastructure upgrades. Nearby cultural sites: Irayankot Mahadeva Temple and St. Theresa Shrine. (Travel And Tour World, Curly Tales)</t>
-        </is>
+      <c r="A4" t="str">
+        <v>Marigold Cultivation Fields</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Seasonal Floral Attraction (Onam flower carpets – Athappookkalam)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Extensively cultivated (up to 50 acres under "Ente Nadu Ente Onam" project), creating vibrant floral landscapes in Kattakada during Onam. (The Times of India, Travel and Food Network)</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Marigold Cultivation Fields</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Seasonal Floral Attraction (Onam flower carpets – Athappookkalam)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Extensively cultivated (up to 50 acres under "Ente Nadu Ente Onam" project), creating vibrant floral landscapes in Kattakada during Onam. (The Times of India, Travel and Food Network)</t>
-        </is>
+      <c r="A5" t="str">
+        <v>Bonacaud &amp; Meenmutty Falls</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Waterfalls, Trekking Trails, Nature Excursions</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Situated in lush green surroundings of Kattakada. Offers tranquil waterfall views and trekking experiences. (Places to Visit)</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bonacaud &amp; Meenmutty Falls</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Waterfalls, Trekking Trails, Nature Excursions</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Situated in lush green surroundings of Kattakada. Offers tranquil waterfall views and trekking experiences. (Places to Visit)</t>
-        </is>
+      <c r="A6" t="str">
+        <v>Aruvikkara Dam</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Reservoir, Boating, Serene Ambience</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Peaceful and scenic dam near Kattakada—ideal for boating and nature lovers. (Places to Visit)</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Aruvikkara Dam</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Reservoir, Boating, Serene Ambience</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Peaceful and scenic dam near Kattakada—ideal for boating and nature lovers. (Places to Visit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Temples &amp; Cultural Sites (Poovachal &amp; Surroundings)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Spiritual / Cultural Heritage</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Includes Padiyanoor Devi Temple (~30 km away in Poovachal) dedicated to Goddess Chamundi with multiple shrines and major festivals like Makam Thozhal, Karthika, etc. (Wikipedia). Also, Pazhavangadi Ganapathy Temple and local churches contribute cultural depth. (Places to Visit)</t>
-        </is>
+      <c r="A7" t="str">
+        <v>Temples &amp; Cultural Sites (Poovachal &amp; Surroundings)</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Spiritual / Cultural Heritage</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Includes Padiyanoor Devi Temple (~30 km away in Poovachal) dedicated to Goddess Chamundi with multiple shrines and major festivals like Makam Thozhal, Karthika, etc. (Wikipedia). Also, Pazhavangadi Ganapathy Temple and local churches contribute cultural depth. (Places to Visit)</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
 </worksheet>
 </file>